--- a/逆合成/hiwo物料-8.xlsx
+++ b/逆合成/hiwo物料-8.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.11.80\立项组\立项组\李伟龙\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="物料信息" sheetId="1" r:id="rId1"/>
@@ -147,10 +152,10 @@
     <t>24孔过滤板-A类型</t>
   </si>
   <si>
-    <t>96孔过滤板</t>
-  </si>
-  <si>
-    <t>GL96-2A01</t>
+    <t>24孔过滤板</t>
+  </si>
+  <si>
+    <t>GL24-2A01</t>
   </si>
   <si>
     <t>A01</t>
@@ -1969,7 +1974,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1989,13 +1994,6 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2486,13 +2484,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2501,118 +2502,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2630,7 +2628,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3038,7 +3036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:23">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3064,7 +3062,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:23">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -3090,7 +3088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:23">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3116,7 +3114,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:23">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -3142,7 +3140,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:23">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3168,7 +3166,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:23">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -3194,7 +3192,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:23">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3220,7 +3218,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:23">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -3246,7 +3244,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:23">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -3272,7 +3270,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:23">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -3298,7 +3296,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:23">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -3397,7 +3395,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:15">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -3417,7 +3415,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:15">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -3437,7 +3435,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:15">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -3457,7 +3455,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:15">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -3477,7 +3475,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:15">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -3497,7 +3495,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:15">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -3517,7 +3515,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:15">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -3537,7 +3535,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:15">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -3557,7 +3555,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:15">
       <c r="A10" s="2">
         <v>1</v>
       </c>
@@ -3577,7 +3575,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:15">
       <c r="A11" s="2">
         <v>1</v>
       </c>
@@ -3597,7 +3595,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:15">
       <c r="A12" s="2">
         <v>1</v>
       </c>
@@ -3617,7 +3615,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:15">
       <c r="A13" s="2">
         <v>1</v>
       </c>
@@ -3637,7 +3635,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:15">
       <c r="A14" s="2">
         <v>2</v>
       </c>
@@ -3657,7 +3655,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:15">
       <c r="A15" s="2">
         <v>2</v>
       </c>
@@ -3677,7 +3675,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:15">
       <c r="A16" s="2">
         <v>2</v>
       </c>
@@ -5257,7 +5255,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:6">
       <c r="A95" s="2">
         <v>8</v>
       </c>
@@ -5274,7 +5272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:6">
       <c r="A96" s="2">
         <v>8</v>
       </c>
@@ -11787,7 +11785,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B10 B14:B29 B31:B53 B55:B62 B63:B78 B80:B86 B87:B94 B183:B187 B279:B283 B375:B379"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B10 B14:B29 B31:B53 B55:B78 B80:B94 B183:B187 B279:B283 B375:B379"/>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
